--- a/reports/devops-juniors-israel-2026-W35.xlsx
+++ b/reports/devops-juniors-israel-2026-W35.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="297">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-25T07:03:40</t>
+    <t xml:space="preserve">2026-08-26T07:04:08</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -103,6 +103,9 @@
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -160,6 +163,24 @@
     <t xml:space="preserve">2026-07-30</t>
   </si>
   <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Team Leader</t>
   </si>
   <si>
@@ -175,9 +196,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux System Administrator</t>
   </si>
   <si>
@@ -274,6 +292,21 @@
     <t xml:space="preserve">2026-07-22</t>
   </si>
   <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
   </si>
   <si>
@@ -328,115 +361,217 @@
     <t xml:space="preserve">2026-08-04</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unilink Ltd.</t>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiliot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 2107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator | Field Position – Company Car Provided!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Octally Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-field-position-%E2%80%93-company-car-provided%21-at-octally-integration-4359515944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Technology Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-unilink-ltd-4446581282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiliot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 2107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-qb-systems-ltd-4451539027</t>
   </si>
   <si>
     <t xml:space="preserve">IT Service Desk Specialist</t>
@@ -454,270 +589,237 @@
     <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
   </si>
   <si>
-    <t xml:space="preserve">SOC Analyst Tier 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log-On Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/soc-analyst-tier-1-at-log-on-software-4453436238</t>
+    <t xml:space="preserve">Lab Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-kaltura-4455279134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4446743008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-technician-at-sqlink-group-4453416679</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-21</t>
   </si>
   <si>
-    <t xml:space="preserve">Finance Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gurugram, India</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8108297?gh_jid=8108297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Helpdesk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Airobotics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-helpdesk-at-airobotics-4439190133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4455188600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Analyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-at-tata-consultancy-services-4449360209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4450505697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0Aisrael-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4455188600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business Systems Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
     <t xml:space="preserve">Automation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6119367004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Power Control System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SolarEdge Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-power-control-system-engineer-at-solaredge-technologies-4438264844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
@@ -745,18 +847,18 @@
     <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
     <t xml:space="preserve">Kubernetes</t>
   </si>
   <si>
@@ -785,6 +887,9 @@
   </si>
   <si>
     <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -924,7 +1029,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -932,7 +1037,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -940,7 +1045,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -948,7 +1053,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="10">
@@ -1030,7 +1135,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
@@ -1038,7 +1143,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -1046,7 +1151,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1058,29 +1163,37 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
+      <c r="A25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="s">
-        <v>29</v>
-      </c>
+      <c r="A26" s="3"/>
       <c r="B26" s="3"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3">
-        <v>25</v>
-      </c>
+      <c r="B27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>11</v>
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="3">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1094,7 +1207,7 @@
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
-    <col min="5" max="5" width="25" customWidth="1"/>
+    <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
     <col min="8" max="8" width="12" customWidth="1"/>
@@ -1104,34 +1217,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
@@ -1139,13 +1252,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>25</v>
@@ -1154,16 +1267,16 @@
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -1171,31 +1284,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
@@ -1203,13 +1316,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>25</v>
@@ -1218,16 +1331,16 @@
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5">
@@ -1241,7 +1354,7 @@
         <v>61</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>25</v>
@@ -1250,16 +1363,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
@@ -1267,31 +1380,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -1299,31 +1412,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F7" s="3">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8">
@@ -1331,7 +1444,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>76</v>
@@ -1340,10 +1453,10 @@
         <v>77</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>78</v>
@@ -1369,25 +1482,25 @@
         <v>82</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9" s="3">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -1395,31 +1508,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>77</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">
@@ -1427,31 +1540,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F11" s="3">
+        <v>70</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="12">
@@ -1459,31 +1572,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F12" s="3">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -1491,31 +1604,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14">
@@ -1529,25 +1642,25 @@
         <v>105</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="15">
@@ -1555,31 +1668,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="3">
+        <v>48</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="3">
-        <v>41</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -1587,31 +1700,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="3">
+        <v>47</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="3">
-        <v>36</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="17">
@@ -1619,31 +1732,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>121</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F17" s="3">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>122</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>123</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>53</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18">
@@ -1651,31 +1764,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19">
@@ -1683,31 +1796,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>71</v>
+        <v>133</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F19" s="3">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>115</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20">
@@ -1715,31 +1828,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="21">
@@ -1747,31 +1860,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>140</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22">
@@ -1779,31 +1892,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="23">
@@ -1811,31 +1924,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>71</v>
+        <v>152</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F23" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24">
@@ -1843,31 +1956,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>53</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25">
@@ -1875,31 +1988,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26">
@@ -1907,31 +2020,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -1972,7 +2085,7 @@
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="31" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="4" max="4" width="25" customWidth="1"/>
+    <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
@@ -1984,48 +2097,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>25</v>
@@ -2034,68 +2147,68 @@
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>25</v>
@@ -2104,22 +2217,22 @@
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="K4" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
@@ -2130,7 +2243,7 @@
         <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>25</v>
@@ -2139,97 +2252,97 @@
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K5" s="3">
-        <v>74</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K6" s="3">
-        <v>28</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E7" s="3">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K7" s="3">
-        <v>0</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>76</v>
@@ -2238,16 +2351,16 @@
         <v>77</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>78</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
@@ -2259,7 +2372,7 @@
         <v>80</v>
       </c>
       <c r="K8" s="3">
-        <v>29</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -2270,171 +2383,171 @@
         <v>82</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E9" s="3">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="K9" s="3">
         <v>30</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="K9" s="3">
-        <v>34</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>77</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E10" s="3">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="K10" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E11" s="3">
+        <v>70</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="K11" s="3">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E12" s="3">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="K12" s="3">
-        <v>56</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E13" s="3">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="K13" s="3">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -2445,203 +2558,203 @@
         <v>105</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>106</v>
+        <v>57</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="K14" s="3">
-        <v>25</v>
+        <v>57</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="3">
+        <v>48</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="3">
-        <v>41</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="K15" s="3">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="3">
+        <v>47</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="3">
-        <v>36</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="K16" s="3">
-        <v>43</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>121</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E17" s="3">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>122</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>123</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="K17" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E18" s="3">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K18" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>71</v>
+        <v>133</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E19" s="3">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>115</v>
+        <v>54</v>
       </c>
       <c r="K19" s="3">
         <v>6</v>
@@ -2649,352 +2762,352 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="K20" s="3">
-        <v>39</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>134</v>
+        <v>57</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>140</v>
+        <v>54</v>
       </c>
       <c r="K21" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="K22" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>71</v>
+        <v>152</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E23" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="K23" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>66</v>
+        <v>88</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>53</v>
+        <v>130</v>
       </c>
       <c r="K24" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K25" s="3">
-        <v>33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="K26" s="3">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E27" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>176</v>
+        <v>155</v>
       </c>
       <c r="K27" s="3">
-        <v>42</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>66</v>
+        <v>175</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>178</v>
+        <v>133</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E28" s="3">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F28" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="G28" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I28" s="3" t="s">
+      <c r="J28" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J28" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="K28" s="3">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>173</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E29" s="3">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>184</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>185</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>85</v>
+        <v>149</v>
       </c>
       <c r="K29" s="3">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
@@ -3005,54 +3118,54 @@
         <v>187</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>134</v>
+        <v>188</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3">
+        <v>20</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K30" s="3">
         <v>12</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="K30" s="3">
-        <v>11</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>192</v>
+        <v>127</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E31" s="3">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>193</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
@@ -3061,77 +3174,77 @@
         <v>194</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>59</v>
+        <v>195</v>
       </c>
       <c r="K31" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>196</v>
+        <v>72</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>173</v>
+        <v>197</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E32" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="K32" s="3">
-        <v>4</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E33" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>204</v>
+        <v>130</v>
       </c>
       <c r="K33" s="3">
         <v>7</v>
@@ -3139,72 +3252,72 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>205</v>
+        <v>136</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>76</v>
+        <v>206</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E34" s="3">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K34" s="3">
-        <v>54</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>134</v>
+        <v>212</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E35" s="3">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>213</v>
+        <v>65</v>
       </c>
       <c r="K35" s="3">
-        <v>36</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -3212,71 +3325,351 @@
         <v>214</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="3">
+        <v>10</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E36" s="3">
-        <v>4</v>
-      </c>
-      <c r="F36" s="3" t="s">
+      <c r="G36" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I36" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="G36" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="J36" s="3" t="s">
-        <v>204</v>
+        <v>48</v>
       </c>
       <c r="K36" s="3">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="C37" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E37" s="3">
+        <v>9</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="G37" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I37" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="J37" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K37" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E37" s="3">
+      <c r="E38" s="3">
+        <v>8</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="K38" s="3">
         <v>0</v>
       </c>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="K37" s="3">
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="3">
+        <v>8</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="K39" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="3">
+        <v>8</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="K40" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" s="3">
+        <v>6</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="K41" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="E42" s="3">
+        <v>4</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="K42" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="K43" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" s="3">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="K44" s="3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="K45" s="3">
+        <v>28</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K37"/>
+  <autoFilter ref="A1:K45"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3314,6 +3707,14 @@
     <hyperlink ref="I35" r:id="rId34"/>
     <hyperlink ref="I36" r:id="rId35"/>
     <hyperlink ref="I37" r:id="rId36"/>
+    <hyperlink ref="I38" r:id="rId37"/>
+    <hyperlink ref="I39" r:id="rId38"/>
+    <hyperlink ref="I40" r:id="rId39"/>
+    <hyperlink ref="I41" r:id="rId40"/>
+    <hyperlink ref="I42" r:id="rId41"/>
+    <hyperlink ref="I43" r:id="rId42"/>
+    <hyperlink ref="I44" r:id="rId43"/>
+    <hyperlink ref="I45" r:id="rId44"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3321,9 +3722,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3332,78 +3733,126 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D2" s="3">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>72</v>
+        <v>122</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>74</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>89</v>
+        <v>164</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>90</v>
+        <v>165</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>91</v>
+        <v>166</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>92</v>
+        <v>167</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>74</v>
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="3">
+        <v>9</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="3">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G3"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
+    <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F5" r:id="rId4"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3418,178 +3867,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>223</v>
+        <v>256</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>224</v>
+        <v>257</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>225</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>226</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>227</v>
+        <v>260</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>228</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>188</v>
+        <v>239</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>206</v>
+        <v>263</v>
       </c>
       <c r="B5" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>230</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>179</v>
+        <v>248</v>
       </c>
       <c r="B6" s="3">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>231</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>232</v>
+        <v>198</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>233</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>211</v>
+        <v>267</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>234</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>235</v>
+        <v>269</v>
       </c>
       <c r="B9" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>236</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>237</v>
+        <v>271</v>
       </c>
       <c r="B10" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>238</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>239</v>
+        <v>273</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>240</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>241</v>
+        <v>275</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>242</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>243</v>
+        <v>277</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>244</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>245</v>
+        <v>279</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>246</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>247</v>
+        <v>281</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>248</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>249</v>
+        <v>283</v>
       </c>
       <c r="B16" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>250</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -3599,20 +4048,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2">
@@ -3620,10 +4069,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>253</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3">
@@ -3631,10 +4080,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>254</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4">
@@ -3642,10 +4091,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>255</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5">
@@ -3656,7 +4105,18 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>256</v>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -3674,51 +4134,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>257</v>
+        <v>292</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>258</v>
+        <v>293</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>259</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>260</v>
+        <v>295</v>
       </c>
       <c r="D2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>260</v>
+        <v>295</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>261</v>
+        <v>296</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>260</v>
+        <v>295</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W35.xlsx
+++ b/reports/devops-juniors-israel-2026-W35.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="253">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-26T07:04:08</t>
+    <t xml:space="preserve">2026-08-27T17:36:46</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -181,45 +181,33 @@
     <t xml:space="preserve">2026-08-20</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nuvoton Technology Israel Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-nuvoton-technology-israel-ltd-4417322206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, GCP, Cloud (any), Docker, Kubernetes, Git, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -229,295 +217,319 @@
     <t xml:space="preserve">2026-06-12</t>
   </si>
   <si>
-    <t xml:space="preserve">Release Engineering Intern (Part-Time, 80%, One-year temporary position)</t>
+    <t xml:space="preserve">Devops Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud System Administrator – AWS/GCP (25559)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, GCP, Cloud (any), Networking, Monitoring, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-system-administrator-%E2%80%93-aws-gcp-25559-at-yael-group-4457268524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Cloud (any), Kubernetes, Networking, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/automation-student-at-radware-4452294600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator &amp; IT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inManage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wiliot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator - 2107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4457742934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lab Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmonic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
   </si>
   <si>
     <t xml:space="preserve">Taboola</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8069193?gh_jid=8069193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">comblack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-comblack-4458201595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, AWS, Azure, Cloud (any), Docker, CI/CD, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4850412101?gh_jid=4850412101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Test Environment Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Cloud (any), CI/CD, Git, Networking, Monitoring, Databases, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/test-environment-support-engineer-at-abra-4442615924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; AI Security Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4932015101?gh_jid=4932015101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-akamai-technologies-4458268923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator &amp; IT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inManage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, GCP, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-it-at-inmanage-4431693143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Operations Engineer I</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Innovid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-engineer-i-at-innovid-4443857656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4377864560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-05-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Systems Engineer - Test &amp; Tools</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wiliot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-systems-engineer-test-tools-at-wiliot-4455788658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator - 2107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-2107-at-tsg-4451506512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extreme</t>
   </si>
   <si>
     <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator | Field Position – Company Car Provided!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Octally Integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-field-position-%E2%80%93-company-car-provided%21-at-octally-integration-4359515944</t>
+    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
   </si>
   <si>
     <t xml:space="preserve">Title</t>
@@ -538,102 +550,6 @@
     <t xml:space="preserve">no</t>
   </si>
   <si>
-    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Technology Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">qb Systems ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-qb-systems-ltd-4451539027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kaltura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-kaltura-4455279134</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tata Consultancy Services</t>
   </si>
   <si>
@@ -646,6 +562,18 @@
     <t xml:space="preserve">2026-08-12</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0Aisrael-at-wavebl-4443917908</t>
+  </si>
+  <si>
     <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
   </si>
   <si>
@@ -658,15 +586,6 @@
     <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior System Administrator</t>
   </si>
   <si>
@@ -688,30 +607,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-technician-at-sqlink-group-4453416679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4455188600</t>
-  </si>
-  <si>
     <t xml:space="preserve">Help Desk Technician</t>
   </si>
   <si>
@@ -727,9 +622,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
     <t xml:space="preserve">Employer Branding Student (Temporary )</t>
   </si>
   <si>
@@ -742,75 +634,51 @@
     <t xml:space="preserve">2026-07-02</t>
   </si>
   <si>
-    <t xml:space="preserve">Service Desk Analyst</t>
+    <t xml:space="preserve">Working Student, Legal (German)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-at-tata-consultancy-services-4449360209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Meitar | Law Offices</t>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4450505697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
@@ -823,6 +691,12 @@
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
   </si>
   <si>
+    <t xml:space="preserve">Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
@@ -841,34 +715,28 @@
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
   </si>
   <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Learn AD module + home lab Windows Server</t>
-  </si>
-  <si>
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -1029,7 +897,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
@@ -1037,7 +905,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1045,7 +913,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -1053,7 +921,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>560</v>
+        <v>557</v>
       </c>
     </row>
     <row r="10">
@@ -1135,7 +1003,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -1143,7 +1011,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
@@ -1151,7 +1019,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1185,7 +1053,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29">
@@ -1193,7 +1061,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1340,7 +1208,7 @@
         <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5">
@@ -1348,13 +1216,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>25</v>
@@ -1363,16 +1231,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -1380,31 +1248,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F6" s="3">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7">
@@ -1412,31 +1280,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="3">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8">
@@ -1444,31 +1312,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="3">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9">
@@ -1476,31 +1344,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F9" s="3">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -1508,31 +1376,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F10" s="3">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -1540,19 +1408,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F11" s="3">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>95</v>
@@ -1564,7 +1432,7 @@
         <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -1572,31 +1440,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F12" s="3">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13">
@@ -1604,31 +1472,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F13" s="3">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14">
@@ -1636,31 +1504,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F14" s="3">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15">
@@ -1668,31 +1536,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F15" s="3">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16">
@@ -1700,31 +1568,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17">
@@ -1732,31 +1600,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18">
@@ -1764,31 +1632,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19">
@@ -1796,19 +1664,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F19" s="3">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>134</v>
@@ -1820,7 +1688,7 @@
         <v>135</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20">
@@ -1834,25 +1702,25 @@
         <v>137</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>57</v>
+        <v>138</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21">
@@ -1860,31 +1728,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>54</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22">
@@ -1892,31 +1760,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23">
@@ -1924,31 +1792,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F23" s="3">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24">
@@ -1956,31 +1824,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25">
@@ -1988,31 +1856,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F25" s="3">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26">
@@ -2020,31 +1888,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>77</v>
+        <v>169</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2097,7 +1965,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -2112,22 +1980,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="2">
@@ -2150,7 +2018,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2162,7 +2030,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -2185,7 +2053,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2197,7 +2065,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -2220,7 +2088,7 @@
         <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2229,21 +2097,21 @@
         <v>59</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>25</v>
@@ -2252,220 +2120,220 @@
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>2</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E6" s="3">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>75</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="3">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="K7" s="3">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="3">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="K8" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E9" s="3">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K9" s="3">
-        <v>30</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E10" s="3">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K10" s="3">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>95</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
@@ -2474,217 +2342,217 @@
         <v>96</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="K11" s="3">
-        <v>6</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E12" s="3">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="K12" s="3">
-        <v>35</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>57</v>
+        <v>106</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E13" s="3">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="K13" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E14" s="3">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="K14" s="3">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>111</v>
+        <v>63</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="3">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="K15" s="3">
-        <v>22</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K16" s="3">
-        <v>87</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E17" s="3">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -2692,60 +2560,60 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>130</v>
+        <v>83</v>
       </c>
       <c r="K18" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E19" s="3">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>134</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
@@ -2754,10 +2622,10 @@
         <v>135</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>54</v>
+        <v>109</v>
       </c>
       <c r="K19" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -2768,908 +2636,523 @@
         <v>137</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>57</v>
+        <v>138</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K20" s="3">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>54</v>
+        <v>147</v>
       </c>
       <c r="K21" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E22" s="3">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K22" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E23" s="3">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K23" s="3">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>136</v>
+        <v>158</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>88</v>
+        <v>133</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E24" s="3">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>130</v>
+        <v>152</v>
       </c>
       <c r="K24" s="3">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E25" s="3">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="K25" s="3">
-        <v>10</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>77</v>
+        <v>169</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="K26" s="3">
-        <v>0</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>174</v>
+        <v>110</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>133</v>
+        <v>169</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="K27" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="K28" s="3">
-        <v>40</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E29" s="3">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>149</v>
+        <v>60</v>
       </c>
       <c r="K29" s="3">
-        <v>15</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>188</v>
+        <v>57</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E30" s="3">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="K30" s="3">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>192</v>
+        <v>50</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>127</v>
+        <v>51</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E31" s="3">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>195</v>
+        <v>103</v>
       </c>
       <c r="K31" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>72</v>
+        <v>198</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E32" s="3">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>200</v>
+        <v>92</v>
       </c>
       <c r="K32" s="3">
-        <v>49</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>202</v>
+        <v>68</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33" s="3">
+        <v>4</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E33" s="3">
-        <v>13</v>
-      </c>
-      <c r="F33" s="3" t="s">
+      <c r="G33" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I33" s="3" t="s">
+      <c r="J33" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="K33" s="3">
-        <v>7</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>136</v>
+        <v>206</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>160</v>
+        <v>208</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E34" s="3">
-        <v>12</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>207</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K34" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E35" s="3">
-        <v>10</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K35" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="3">
-        <v>10</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="K36" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E37" s="3">
-        <v>9</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K37" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E38" s="3">
-        <v>8</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K38" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="3">
-        <v>8</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="K39" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E40" s="3">
-        <v>8</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="K40" s="3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E41" s="3">
-        <v>6</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="K41" s="3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E42" s="3">
-        <v>4</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="K42" s="3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E43" s="3">
-        <v>3</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="K43" s="3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E44" s="3">
-        <v>3</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="K44" s="3">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="K45" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K45"/>
+  <autoFilter ref="A1:K34"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3704,17 +3187,6 @@
     <hyperlink ref="I32" r:id="rId31"/>
     <hyperlink ref="I33" r:id="rId32"/>
     <hyperlink ref="I34" r:id="rId33"/>
-    <hyperlink ref="I35" r:id="rId34"/>
-    <hyperlink ref="I36" r:id="rId35"/>
-    <hyperlink ref="I37" r:id="rId36"/>
-    <hyperlink ref="I38" r:id="rId37"/>
-    <hyperlink ref="I39" r:id="rId38"/>
-    <hyperlink ref="I40" r:id="rId39"/>
-    <hyperlink ref="I41" r:id="rId40"/>
-    <hyperlink ref="I42" r:id="rId41"/>
-    <hyperlink ref="I43" r:id="rId42"/>
-    <hyperlink ref="I44" r:id="rId43"/>
-    <hyperlink ref="I45" r:id="rId44"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3722,9 +3194,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="1" max="1" width="46" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3745,10 +3217,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -3756,103 +3228,79 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>121</v>
+        <v>79</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>122</v>
+        <v>81</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>123</v>
+        <v>82</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>165</v>
+        <v>125</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>166</v>
+        <v>126</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>167</v>
+        <v>127</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>217</v>
+        <v>128</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>218</v>
+        <v>129</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>219</v>
+        <v>131</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>220</v>
+        <v>132</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="3">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>124</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G4"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3867,178 +3315,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>256</v>
+        <v>211</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>257</v>
+        <v>212</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>258</v>
+        <v>213</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="B2" s="3">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>259</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>260</v>
+        <v>216</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>261</v>
+        <v>217</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
       <c r="B4" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>262</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>263</v>
+        <v>184</v>
       </c>
       <c r="B5" s="3">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>264</v>
+        <v>219</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>248</v>
+        <v>220</v>
       </c>
       <c r="B6" s="3">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>265</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>198</v>
+        <v>164</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>266</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>267</v>
+        <v>223</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>268</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>269</v>
+        <v>225</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>270</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>271</v>
+        <v>227</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>272</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>273</v>
+        <v>229</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>274</v>
+        <v>230</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>275</v>
+        <v>231</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>276</v>
+        <v>232</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="B13" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>278</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>279</v>
+        <v>235</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>280</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>281</v>
+        <v>237</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>282</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>283</v>
+        <v>239</v>
       </c>
       <c r="B16" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>284</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -4058,10 +3506,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>285</v>
+        <v>241</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>286</v>
+        <v>242</v>
       </c>
     </row>
     <row r="2">
@@ -4069,10 +3517,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>287</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3">
@@ -4080,10 +3528,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>288</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4">
@@ -4091,10 +3539,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>289</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5">
@@ -4105,7 +3553,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>290</v>
+        <v>246</v>
       </c>
     </row>
     <row r="6">
@@ -4116,7 +3564,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>291</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -4137,13 +3585,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>293</v>
+        <v>249</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>294</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2">
@@ -4151,10 +3599,10 @@
         <v>32</v>
       </c>
       <c r="B2" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>295</v>
+        <v>251</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4163,22 +3611,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>295</v>
+        <v>251</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>296</v>
+        <v>252</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>295</v>
+        <v>251</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W35.xlsx
+++ b/reports/devops-juniors-israel-2026-W35.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="297">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-27T17:36:46</t>
+    <t xml:space="preserve">2026-08-28T18:35:27</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -91,12 +91,12 @@
     <t xml:space="preserve">By bucket</t>
   </si>
   <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
@@ -235,21 +235,6 @@
     <t xml:space="preserve">2026-07-27</t>
   </si>
   <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud System Administrator – AWS/GCP (25559)</t>
   </si>
   <si>
@@ -280,6 +265,24 @@
     <t xml:space="preserve">2026-07-22</t>
   </si>
   <si>
+    <t xml:space="preserve">Computer System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computer-system-engineer-at-camtek-4432772061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-02</t>
+  </si>
+  <si>
     <t xml:space="preserve">Automation Student</t>
   </si>
   <si>
@@ -346,6 +349,24 @@
     <t xml:space="preserve">2026-08-19</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Operations &amp; Security Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PointFive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-operations-security-specialist-at-pointfive-4426311043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Operator</t>
   </si>
   <si>
@@ -361,6 +382,39 @@
     <t xml:space="preserve">2026-07-13</t>
   </si>
   <si>
+    <t xml:space="preserve">IT Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinomenal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bnei Brak, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-specialist-at-spinomenal-4431228721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Azure, Cloud (any), Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-administrator-at-check-point-software-4458547603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-28</t>
+  </si>
+  <si>
     <t xml:space="preserve">Gini-Apps</t>
   </si>
   <si>
@@ -388,33 +442,6 @@
     <t xml:space="preserve">2026-08-11</t>
   </si>
   <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4457742934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
     <t xml:space="preserve">abra</t>
   </si>
   <si>
@@ -424,24 +451,42 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
   </si>
   <si>
+    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
+  </si>
+  <si>
     <t xml:space="preserve">Data Center IT Technician - Masmiya</t>
   </si>
   <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-masmiya-at-nebius-4437672340</t>
   </si>
   <si>
     <t xml:space="preserve">2026-07-17</t>
   </si>
   <si>
+    <t xml:space="preserve">Information Technology Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qb Systems ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/information-technology-support-engineer-at-qb-systems-ltd-4451539027</t>
+  </si>
+  <si>
     <t xml:space="preserve">IT Service Desk Specialist</t>
   </si>
   <si>
@@ -457,231 +502,318 @@
     <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8527726002?gh_jid=8527726002</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lab Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harmonic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/lab-support-engineer-at-harmonic-4448547160</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-help-desk-technician-at-energean-4443137036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-23</t>
+    <t xml:space="preserve">Technical Support Engineer - Entry Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-entry-level-at-check-point-software-4441459886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">איש/אשת תמיכה טכנית ו -Helpdesk 2+בפתח תקווה</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arad Tech - Technology, Engineering &amp; AI Recruitment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Networking, Virtualization, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/%D7%90%D7%99%D7%A9-%D7%90%D7%A9%D7%AA-%D7%AA%D7%9E%D7%99%D7%9B%D7%94-%D7%98%D7%9B%D7%A0%D7%99%D7%AA-%D7%95-helpdesk-2%2B%D7%91%D7%A4%D7%AA%D7%97-%D7%AA%D7%A7%D7%95%D7%95%D7%94-at-arad-tech-technology-engineering-ai-recruitment-4440622529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support- IL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-il-at-cyera-4457888968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-08</t>
   </si>
   <si>
     <t xml:space="preserve">Help Desk</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-abra-4449365989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Analyst Intern – Advertising Optimization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8041366?gh_jid=8041366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-08</t>
+    <t xml:space="preserve">Kaltura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-at-kaltura-4455279134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estonia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
   </si>
   <si>
     <t xml:space="preserve">Help Desk Specialist</t>
   </si>
   <si>
-    <t xml:space="preserve">Extreme</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Virtualization, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-extreme-4443366080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
     <t xml:space="preserve">Tata Consultancy Services</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4446743008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
+    <t xml:space="preserve">Networking, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-specialist-at-tata-consultancy-services-4446732076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COM-C-TECH LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Windows Server</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4455188600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AudioCodes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk Support Specialist (37425)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-37425-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4459686882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Technician</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-technician-at-abra-4454760617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Desk Analyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/service-desk-analyst-at-tata-consultancy-services-4449360209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help desk &amp; PC טכנאי/ת</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meitar | Law Offices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-pc-%D7%98%D7%9B%D7%A0%D7%90%D7%99-%D7%AA-at-meitar-law-offices-4450505697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk &amp; Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tipuli Tech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-support-specialist-at-tipuli-tech-4447121790</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist for ROETO - Position No. 1717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBI Investment House</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-for-roeto-position-no-1717-at-ibi-investment-house-4451193725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comblack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-comblack-4459887000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TECEZE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-support-engineer-at-teceze-4458365687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0Aisrael-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProdOps &amp; Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estonia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4865066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COM-C-TECH LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-com-c-tech-ltd-4457234117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk Technician</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AudioCodes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Yehuda, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/help-desk-technician-at-audiocodes-4454240269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
     <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
   </si>
   <si>
@@ -703,52 +835,52 @@
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Git</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search 'free &lt;skill&gt; tutorial' on YouTube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Git</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pro Git book (free online) + create a learning repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
     <t xml:space="preserve">Count</t>
   </si>
   <si>
     <t xml:space="preserve">Pivot path advice</t>
   </si>
   <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
   </si>
   <si>
     <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
@@ -897,7 +1029,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -905,7 +1037,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -913,7 +1045,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -921,7 +1053,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="10">
@@ -1003,7 +1135,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
@@ -1011,7 +1143,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
@@ -1019,7 +1151,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -1053,7 +1185,7 @@
         <v>31</v>
       </c>
       <c r="B28" s="3">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
@@ -1073,7 +1205,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="3" max="3" width="54" customWidth="1"/>
     <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1129,7 +1261,7 @@
         <v>45</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1193,7 +1325,7 @@
         <v>57</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
@@ -1225,7 +1357,7 @@
         <v>63</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
@@ -1289,10 +1421,10 @@
         <v>75</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>76</v>
@@ -1304,7 +1436,7 @@
         <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1312,31 +1444,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="3">
+        <v>60</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="3">
-        <v>68</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="9">
@@ -1344,31 +1476,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -1376,10 +1508,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>63</v>
@@ -1391,16 +1523,16 @@
         <v>52</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11">
@@ -1408,31 +1540,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>63</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3">
         <v>52</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="12">
@@ -1440,13 +1572,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>29</v>
@@ -1455,16 +1587,16 @@
         <v>46</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
@@ -1472,13 +1604,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>28</v>
@@ -1487,16 +1619,16 @@
         <v>41</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14">
@@ -1504,31 +1636,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15">
@@ -1536,31 +1668,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>63</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -1568,31 +1700,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17">
@@ -1600,31 +1732,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>63</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>83</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18">
@@ -1632,31 +1764,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>130</v>
+        <v>63</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -1664,31 +1796,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20">
@@ -1696,31 +1828,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F20" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21">
@@ -1728,31 +1860,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F21" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
     </row>
     <row r="22">
@@ -1760,22 +1892,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="3">
+        <v>23</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="3">
-        <v>17</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
@@ -1798,13 +1930,13 @@
         <v>154</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F23" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>155</v>
@@ -1816,7 +1948,7 @@
         <v>156</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24">
@@ -1824,31 +1956,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="D24" s="3" t="s">
-        <v>100</v>
+        <v>159</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25">
@@ -1856,31 +1988,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F25" s="3">
+        <v>20</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F25" s="3">
-        <v>13</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>166</v>
+        <v>116</v>
       </c>
     </row>
     <row r="26">
@@ -1888,31 +2020,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="E26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F26" s="3">
+        <v>20</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" s="3">
-        <v>13</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -1951,7 +2083,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="2" max="2" width="54" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -1965,7 +2097,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>35</v>
@@ -1980,22 +2112,22 @@
         <v>38</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>173</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>174</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>40</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2">
@@ -2009,7 +2141,7 @@
         <v>45</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2018,7 +2150,7 @@
         <v>46</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>32</v>
@@ -2030,7 +2162,7 @@
         <v>48</v>
       </c>
       <c r="K2" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -2053,7 +2185,7 @@
         <v>52</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>31</v>
@@ -2065,7 +2197,7 @@
         <v>54</v>
       </c>
       <c r="K3" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -2079,7 +2211,7 @@
         <v>57</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
@@ -2088,7 +2220,7 @@
         <v>58</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>31</v>
@@ -2100,7 +2232,7 @@
         <v>60</v>
       </c>
       <c r="K4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -2114,7 +2246,7 @@
         <v>63</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E5" s="3">
         <v>100</v>
@@ -2123,7 +2255,7 @@
         <v>64</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>31</v>
@@ -2135,7 +2267,7 @@
         <v>66</v>
       </c>
       <c r="K5" s="3">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6">
@@ -2158,7 +2290,7 @@
         <v>70</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2170,7 +2302,7 @@
         <v>72</v>
       </c>
       <c r="K6" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7">
@@ -2184,16 +2316,16 @@
         <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E7" s="3">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>31</v>
@@ -2202,88 +2334,88 @@
         <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="K7" s="3">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E8" s="3">
+        <v>60</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="3">
-        <v>68</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="C9" s="3" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E9" s="3">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K9" s="3">
-        <v>36</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>63</v>
@@ -2295,68 +2427,68 @@
         <v>52</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K10" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>63</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E11" s="3">
         <v>52</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K11" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>29</v>
@@ -2365,33 +2497,33 @@
         <v>46</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>28</v>
@@ -2400,159 +2532,159 @@
         <v>41</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K13" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E14" s="3">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K14" s="3">
-        <v>45</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>63</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E15" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="K15" s="3">
-        <v>7</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="K16" s="3">
-        <v>16</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>63</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>83</v>
+        <v>132</v>
       </c>
       <c r="K17" s="3">
         <v>0</v>
@@ -2560,165 +2692,165 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>130</v>
+        <v>63</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E18" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="K18" s="3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>110</v>
+        <v>136</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>109</v>
+        <v>141</v>
       </c>
       <c r="K19" s="3">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="K20" s="3">
-        <v>41</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E21" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="K21" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="3">
+        <v>23</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E22" s="3">
-        <v>17</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="G22" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>31</v>
@@ -2730,7 +2862,7 @@
         <v>152</v>
       </c>
       <c r="K22" s="3">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
@@ -2741,19 +2873,19 @@
         <v>154</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="3">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>155</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>31</v>
@@ -2762,138 +2894,138 @@
         <v>156</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="K23" s="3">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="C24" s="3" t="s">
-        <v>100</v>
+        <v>159</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>152</v>
+        <v>116</v>
       </c>
       <c r="K24" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>162</v>
+        <v>129</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E25" s="3">
+        <v>20</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E25" s="3">
-        <v>13</v>
-      </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>166</v>
+        <v>116</v>
       </c>
       <c r="K25" s="3">
-        <v>50</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="D26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E26" s="3">
+        <v>20</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="G26" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="3">
-        <v>13</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="G26" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="K26" s="3">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>110</v>
+        <v>177</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>178</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>169</v>
+        <v>113</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>179</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>31</v>
@@ -2902,257 +3034,642 @@
         <v>180</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>181</v>
+        <v>60</v>
       </c>
       <c r="K27" s="3">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E28" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>184</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>185</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
       <c r="K28" s="3">
-        <v>13</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>188</v>
+        <v>124</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="K29" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>57</v>
+        <v>193</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>103</v>
+        <v>60</v>
       </c>
       <c r="K30" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>50</v>
+        <v>197</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="K31" s="3">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>199</v>
+        <v>57</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E32" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>31</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="K32" s="3">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E33" s="3">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>205</v>
+        <v>104</v>
       </c>
       <c r="K33" s="3">
-        <v>56</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>208</v>
+        <v>167</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="3">
+        <v>8</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="K34" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E35" s="3">
+        <v>6</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K35" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E36" s="3">
+        <v>6</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="K36" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E37" s="3">
+        <v>6</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="K37" s="3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E38" s="3">
+        <v>4</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="K38" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="3">
+        <v>3</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="K39" s="3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E40" s="3">
+        <v>3</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="K40" s="3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="K41" s="3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="3">
+        <v>3</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="K42" s="3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" s="3">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="K43" s="3">
         <v>0</v>
       </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H34" s="3" t="s">
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" s="3">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="K44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H45" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I34" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="K34" s="3">
-        <v>29</v>
+      <c r="I45" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="K45" s="3">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K34"/>
+  <autoFilter ref="A1:K45"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3187,6 +3704,17 @@
     <hyperlink ref="I32" r:id="rId31"/>
     <hyperlink ref="I33" r:id="rId32"/>
     <hyperlink ref="I34" r:id="rId33"/>
+    <hyperlink ref="I35" r:id="rId34"/>
+    <hyperlink ref="I36" r:id="rId35"/>
+    <hyperlink ref="I37" r:id="rId36"/>
+    <hyperlink ref="I38" r:id="rId37"/>
+    <hyperlink ref="I39" r:id="rId38"/>
+    <hyperlink ref="I40" r:id="rId39"/>
+    <hyperlink ref="I41" r:id="rId40"/>
+    <hyperlink ref="I42" r:id="rId41"/>
+    <hyperlink ref="I43" r:id="rId42"/>
+    <hyperlink ref="I44" r:id="rId43"/>
+    <hyperlink ref="I45" r:id="rId44"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3194,8 +3722,8 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="46" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
@@ -3217,10 +3745,10 @@
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>42</v>
@@ -3228,79 +3756,103 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>68</v>
+        <v>30</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>82</v>
+        <v>131</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>83</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>124</v>
+        <v>217</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>125</v>
+        <v>218</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>126</v>
+        <v>215</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>127</v>
+        <v>219</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>83</v>
+        <v>132</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>128</v>
+        <v>212</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>129</v>
+        <v>245</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>131</v>
+        <v>227</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>83</v>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F5" r:id="rId4"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3315,178 +3867,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>211</v>
+        <v>256</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>212</v>
+        <v>257</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>213</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="B2" s="3">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>215</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="B3" s="3">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>217</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>218</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>184</v>
+        <v>262</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>219</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>220</v>
+        <v>264</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>221</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>222</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>223</v>
+        <v>267</v>
       </c>
       <c r="B8" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>224</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>225</v>
+        <v>269</v>
       </c>
       <c r="B9" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>226</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>227</v>
+        <v>271</v>
       </c>
       <c r="B10" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>228</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>229</v>
+        <v>273</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>230</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>231</v>
+        <v>275</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>232</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>233</v>
+        <v>277</v>
       </c>
       <c r="B13" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>234</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>235</v>
+        <v>279</v>
       </c>
       <c r="B14" s="3">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>236</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>237</v>
+        <v>281</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>238</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>239</v>
+        <v>283</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>240</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -3506,10 +4058,10 @@
         <v>37</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>241</v>
+        <v>285</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>242</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2">
@@ -3517,10 +4069,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>243</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3">
@@ -3528,10 +4080,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>244</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4">
@@ -3539,10 +4091,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>245</v>
+        <v>289</v>
       </c>
     </row>
     <row r="5">
@@ -3553,7 +4105,7 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>246</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6">
@@ -3564,7 +4116,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>247</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -3585,13 +4137,13 @@
         <v>40</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>248</v>
+        <v>292</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>249</v>
+        <v>293</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>250</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2">
@@ -3602,7 +4154,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -3611,22 +4163,22 @@
         <v>31</v>
       </c>
       <c r="B3" s="3">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>252</v>
+        <v>296</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="D4" s="3"/>
     </row>
